--- a/XBRL-template-MPERS/Group/08-SOCF-Direct.xlsx
+++ b/XBRL-template-MPERS/Group/08-SOCF-Direct.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -470,579 +470,544 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Disclosure on statement of cash flows [abstract]</t>
+          <t>Disclosure on statement of cash flows</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Statement of cash flows [abstract]</t>
+          <t>Statement of cash flows</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Statement of cash flows [table]</t>
+          <t>Statement of cash flows</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Consolidated and separate financial statements [axis]</t>
+          <t>Cash flows from (used in) operating activities</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Group [member]</t>
+          <t>Classes of cash receipts from operating activities</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Company [member]</t>
+          <t>Receipts from sales of goods and rendering of services</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Statement of cash flows [line items]</t>
+          <t>Receipts from royalties, fees, commissions and other revenue</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Statement of cash flows [abstract]</t>
+          <t>Other cash receipts from operating activities</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cash flows from (used in) operating activities [abstract]</t>
+          <t>Classes of cash payments from operating activities</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Classes of cash receipts from operating activities [abstract]</t>
+          <t>Payments to suppliers for goods and services</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Receipts from sales of goods and rendering of services</t>
+          <t>Payments to and on behalf of employees</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Receipts from royalties, fees, commissions and other revenue</t>
+          <t>Other cash payments from operating activities</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Other cash receipts from operating activities</t>
+          <t>Cash generated from (used in) operating activities</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Classes of cash payments from operating activities [abstract]</t>
+          <t>Dividends paid</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Payments to suppliers for goods and services</t>
+          <t>Dividends received</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Payments to and on behalf of employees</t>
+          <t>Interest paid</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Other cash payments from operating activities</t>
+          <t>Interest received</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cash generated from (used in) operating activities</t>
+          <t>Income taxes refund (paid)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dividends paid</t>
+          <t>Other cash inflows (outflows) from operating activities</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Dividends received</t>
-        </is>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>*Net cash flows from (used in) operating activities</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>1*B8+1*B9+1*B10+1*B12+1*B13+1*B14+1*B16+1*B17+1*B18+1*B19+1*B20+1*B21+1*B15</f>
+        <v/>
+      </c>
+      <c r="C22">
+        <f>1*C8+1*C9+1*C10+1*C12+1*C13+1*C14+1*C16+1*C17+1*C18+1*C19+1*C20+1*C21+1*C15</f>
+        <v/>
+      </c>
+      <c r="D22">
+        <f>1*D8+1*D9+1*D10+1*D12+1*D13+1*D14+1*D16+1*D17+1*D18+1*D19+1*D20+1*D21+1*D15</f>
+        <v/>
+      </c>
+      <c r="E22">
+        <f>1*E8+1*E9+1*E10+1*E12+1*E13+1*E14+1*E16+1*E17+1*E18+1*E19+1*E20+1*E21+1*E15</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Interest paid</t>
+          <t>Cash flows from (used in) investing activities</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Interest received</t>
+          <t>Proceeds from disposal of subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Income taxes refund (paid)</t>
+          <t>Acquisition and subscription of shares in subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Other cash inflows (outflows) from operating activities</t>
+          <t>Proceeds from disposal of joint ventures</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>*Net cash flows from (used in) operating activities</t>
-        </is>
-      </c>
-      <c r="B27">
-        <f>1*B13+1*B14+1*B15+1*B17+1*B18+1*B19+1*B21+1*B22+1*B23+1*B24+1*B25+1*B26+1*B20</f>
-        <v/>
-      </c>
-      <c r="C27">
-        <f>1*C13+1*C14+1*C15+1*C17+1*C18+1*C19+1*C21+1*C22+1*C23+1*C24+1*C25+1*C26+1*C20</f>
-        <v/>
-      </c>
-      <c r="D27">
-        <f>1*D13+1*D14+1*D15+1*D17+1*D18+1*D19+1*D21+1*D22+1*D23+1*D24+1*D25+1*D26+1*D20</f>
-        <v/>
-      </c>
-      <c r="E27">
-        <f>1*E13+1*E14+1*E15+1*E17+1*E18+1*E19+1*E21+1*E22+1*E23+1*E24+1*E25+1*E26+1*E20</f>
-        <v/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Acquisition and subscription of shares in joint ventures</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cash flows from (used in) investing activities [abstract]</t>
+          <t>Other cash receipts from sales of equity or debt instruments of other entities</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Proceeds from disposal of subsidiaries</t>
+          <t>Other cash payments to acquire equity or debt instruments of other entities</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Acquisition and subscription of shares in subsidiaries</t>
+          <t>Proceeds from sales of property, plant and equipment</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Proceeds from disposal of joint ventures</t>
+          <t>Purchase of property, plant and equipment</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Acquisition and subscription of shares in joint ventures</t>
+          <t>Proceeds from sales of intangible assets</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Other cash receipts from sales of equity or debt instruments of other entities</t>
+          <t>Purchase of intangible assets</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Other cash payments to acquire equity or debt instruments of other entities</t>
+          <t>Proceeds from sales of other long-term assets</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Proceeds from sales of property, plant and equipment</t>
+          <t>Purchase of other long-term assets</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Purchase of property, plant and equipment</t>
+          <t>Cash advances and loans made to other parties</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Proceeds from sales of intangible assets</t>
+          <t>Cash receipts from repayment of advances and loans made to other parties</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Purchase of intangible assets</t>
+          <t>Cash payments for futures contracts, forward contracts, option contracts and swap contracts</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Proceeds from sales of other long-term assets</t>
+          <t>Cash receipts from futures contracts, forward contracts, option contracts and swap contracts</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Purchase of other long-term assets</t>
+          <t>Dividends received</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cash advances and loans made to other parties</t>
+          <t>Interest received</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cash receipts from repayment of advances and loans made to other parties</t>
+          <t>Other cash inflows (outflows) from investing activities</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Cash payments for futures contracts, forward contracts, option contracts and swap contracts</t>
-        </is>
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>*Net cash flows from (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="B43">
+        <f>1*B24+-1*B25+1*B28+-1*B29+1*B26+-1*B27+1*B30+-1*B31+1*B32+-1*B33+1*B34+-1*B35+-1*B36+1*B37+-1*B38+1*B39+1*B40+1*B41+1*B42</f>
+        <v/>
+      </c>
+      <c r="C43">
+        <f>1*C24+-1*C25+1*C28+-1*C29+1*C26+-1*C27+1*C30+-1*C31+1*C32+-1*C33+1*C34+-1*C35+-1*C36+1*C37+-1*C38+1*C39+1*C40+1*C41+1*C42</f>
+        <v/>
+      </c>
+      <c r="D43">
+        <f>1*D24+-1*D25+1*D28+-1*D29+1*D26+-1*D27+1*D30+-1*D31+1*D32+-1*D33+1*D34+-1*D35+-1*D36+1*D37+-1*D38+1*D39+1*D40+1*D41+1*D42</f>
+        <v/>
+      </c>
+      <c r="E43">
+        <f>1*E24+-1*E25+1*E28+-1*E29+1*E26+-1*E27+1*E30+-1*E31+1*E32+-1*E33+1*E34+-1*E35+-1*E36+1*E37+-1*E38+1*E39+1*E40+1*E41+1*E42</f>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cash receipts from futures contracts, forward contracts, option contracts and swap contracts</t>
+          <t>Cash flows from (used in) financing activities</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Dividends received</t>
+          <t>Proceeds from issuing shares</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Interest received</t>
+          <t>Proceeds from issuing other equity instruments</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Other cash inflows (outflows) from investing activities</t>
+          <t>Payments to acquire or redeem entity's shares</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>*Net cash flows from (used in) investing activities</t>
-        </is>
-      </c>
-      <c r="B48">
-        <f>1*B29+-1*B30+1*B33+-1*B34+1*B31+-1*B32+1*B35+-1*B36+1*B37+-1*B38+1*B39+-1*B40+-1*B41+1*B42+-1*B43+1*B44+1*B45+1*B46+1*B47</f>
-        <v/>
-      </c>
-      <c r="C48">
-        <f>1*C29+-1*C30+1*C33+-1*C34+1*C31+-1*C32+1*C35+-1*C36+1*C37+-1*C38+1*C39+-1*C40+-1*C41+1*C42+-1*C43+1*C44+1*C45+1*C46+1*C47</f>
-        <v/>
-      </c>
-      <c r="D48">
-        <f>1*D29+-1*D30+1*D33+-1*D34+1*D31+-1*D32+1*D35+-1*D36+1*D37+-1*D38+1*D39+-1*D40+-1*D41+1*D42+-1*D43+1*D44+1*D45+1*D46+1*D47</f>
-        <v/>
-      </c>
-      <c r="E48">
-        <f>1*E29+-1*E30+1*E33+-1*E34+1*E31+-1*E32+1*E35+-1*E36+1*E37+-1*E38+1*E39+-1*E40+-1*E41+1*E42+-1*E43+1*E44+1*E45+1*E46+1*E47</f>
-        <v/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Payments to acquire other equity instruments</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cash flows from (used in) financing activities [abstract]</t>
+          <t>Proceeds from borrowings</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Proceeds from issuing shares</t>
+          <t>Repayments of borrowings</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Proceeds from issuing other equity instruments</t>
+          <t>Repayment of loan from associate</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Payments to acquire or redeem entity's shares</t>
+          <t>Payments of finance lease liabilities</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Payments to acquire other equity instruments</t>
+          <t>Dividends paid</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Proceeds from borrowings</t>
+          <t>Interest paid</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Repayments of borrowings</t>
+          <t>Other cash inflows (outflows) from financing activities</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Repayment of loan from associate</t>
-        </is>
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>*Net cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="B56">
+        <f>1*B45+1*B46+-1*B47+-1*B48+1*B49+-1*B50+-1*B51+-1*B52+-1*B53+-1*B54+1*B55</f>
+        <v/>
+      </c>
+      <c r="C56">
+        <f>1*C45+1*C46+-1*C47+-1*C48+1*C49+-1*C50+-1*C51+-1*C52+-1*C53+-1*C54+1*C55</f>
+        <v/>
+      </c>
+      <c r="D56">
+        <f>1*D45+1*D46+-1*D47+-1*D48+1*D49+-1*D50+-1*D51+-1*D52+-1*D53+-1*D54+1*D55</f>
+        <v/>
+      </c>
+      <c r="E56">
+        <f>1*E45+1*E46+-1*E47+-1*E48+1*E49+-1*E50+-1*E51+-1*E52+-1*E53+-1*E54+1*E55</f>
+        <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Payments of finance lease liabilities</t>
-        </is>
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>*Net increase (decrease) in cash and cash equivalents before effect of exchange rate changes</t>
+        </is>
+      </c>
+      <c r="B57">
+        <f>1*B22+1*B43+1*B56</f>
+        <v/>
+      </c>
+      <c r="C57">
+        <f>1*C22+1*C43+1*C56</f>
+        <v/>
+      </c>
+      <c r="D57">
+        <f>1*D22+1*D43+1*D56</f>
+        <v/>
+      </c>
+      <c r="E57">
+        <f>1*E22+1*E43+1*E56</f>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Dividends paid</t>
+          <t>Effect of exchange rate changes on cash and cash equivalents</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Interest paid</t>
-        </is>
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>*Net increase (decrease) in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B59">
+        <f>1*B57+1*B58</f>
+        <v/>
+      </c>
+      <c r="C59">
+        <f>1*C57+1*C58</f>
+        <v/>
+      </c>
+      <c r="D59">
+        <f>1*D57+1*D58</f>
+        <v/>
+      </c>
+      <c r="E59">
+        <f>1*E57+1*E58</f>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Other cash inflows (outflows) from financing activities</t>
+          <t>Cash and cash equivalents at beginning of period</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>*Net cash flows from (used in) financing activities</t>
-        </is>
-      </c>
-      <c r="B61">
-        <f>1*B50+1*B51+-1*B52+-1*B53+1*B54+-1*B55+-1*B56+-1*B57+-1*B58+-1*B59+1*B60</f>
-        <v/>
-      </c>
-      <c r="C61">
-        <f>1*C50+1*C51+-1*C52+-1*C53+1*C54+-1*C55+-1*C56+-1*C57+-1*C58+-1*C59+1*C60</f>
-        <v/>
-      </c>
-      <c r="D61">
-        <f>1*D50+1*D51+-1*D52+-1*D53+1*D54+-1*D55+-1*D56+-1*D57+-1*D58+-1*D59+1*D60</f>
-        <v/>
-      </c>
-      <c r="E61">
-        <f>1*E50+1*E51+-1*E52+-1*E53+1*E54+-1*E55+-1*E56+-1*E57+-1*E58+-1*E59+1*E60</f>
-        <v/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of period</t>
+        </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>*Net increase (decrease) in cash and cash equivalents before effect of exchange rate changes</t>
-        </is>
-      </c>
-      <c r="B62">
-        <f>1*B27+1*B48+1*B61</f>
-        <v/>
-      </c>
-      <c r="C62">
-        <f>1*C27+1*C48+1*C61</f>
-        <v/>
-      </c>
-      <c r="D62">
-        <f>1*D27+1*D48+1*D61</f>
-        <v/>
-      </c>
-      <c r="E62">
-        <f>1*E27+1*E48+1*E61</f>
-        <v/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Details of cash flows</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Effect of exchange rate changes on cash and cash equivalents</t>
+          <t>Cash and cash equivalents</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>*Net increase (decrease) in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="B64">
-        <f>1*B62+1*B63</f>
-        <v/>
-      </c>
-      <c r="C64">
-        <f>1*C62+1*C63</f>
-        <v/>
-      </c>
-      <c r="D64">
-        <f>1*D62+1*D63</f>
-        <v/>
-      </c>
-      <c r="E64">
-        <f>1*E62+1*E63</f>
-        <v/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Bank overdrafts</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at beginning of period</t>
+          <t>Other adjustments to reconcile cash and cash equivalents</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents at end of period</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Details of cash flows [abstract]</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Bank overdrafts</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Other adjustments to reconcile cash and cash equivalents</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="inlineStr">
+      <c r="A66" s="1" t="inlineStr">
         <is>
           <t>*Cash and cash equivalents at end of period</t>
         </is>
       </c>
-      <c r="B71">
-        <f>1*B68+-1*B69+1*B70</f>
-        <v/>
-      </c>
-      <c r="C71">
-        <f>1*C68+-1*C69+1*C70</f>
-        <v/>
-      </c>
-      <c r="D71">
-        <f>1*D68+-1*D69+1*D70</f>
-        <v/>
-      </c>
-      <c r="E71">
-        <f>1*E68+-1*E69+1*E70</f>
+      <c r="B66">
+        <f>1*B63+-1*B64+1*B65</f>
+        <v/>
+      </c>
+      <c r="C66">
+        <f>1*C63+-1*C64+1*C65</f>
+        <v/>
+      </c>
+      <c r="D66">
+        <f>1*D63+-1*D64+1*D65</f>
+        <v/>
+      </c>
+      <c r="E66">
+        <f>1*E63+-1*E64+1*E65</f>
         <v/>
       </c>
     </row>

--- a/XBRL-template-MPERS/Group/08-SOCF-Direct.xlsx
+++ b/XBRL-template-MPERS/Group/08-SOCF-Direct.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,14 +27,24 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1F3864"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +59,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -468,35 +479,35 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Disclosure on statement of cash flows</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Statement of cash flows</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Statement of cash flows</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Cash flows from (used in) operating activities</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Classes of cash receipts from operating activities</t>
         </is>
@@ -524,7 +535,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Classes of cash payments from operating activities</t>
         </is>
@@ -601,7 +612,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>*Net cash flows from (used in) operating activities</t>
         </is>
@@ -624,7 +635,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>Cash flows from (used in) investing activities</t>
         </is>
@@ -764,7 +775,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>*Net cash flows from (used in) investing activities</t>
         </is>
@@ -787,7 +798,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>Cash flows from (used in) financing activities</t>
         </is>
@@ -871,7 +882,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>*Net cash flows from (used in) financing activities</t>
         </is>
@@ -894,7 +905,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>*Net increase (decrease) in cash and cash equivalents before effect of exchange rate changes</t>
         </is>
@@ -924,7 +935,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>*Net increase (decrease) in cash and cash equivalents</t>
         </is>
@@ -961,7 +972,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="1" t="inlineStr">
         <is>
           <t>Details of cash flows</t>
         </is>
@@ -989,7 +1000,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>*Cash and cash equivalents at end of period</t>
         </is>
